--- a/labs/lab-07-surface-attrition-insights-with-copilot-and-advanced-analysis/data/BrightPath_Attrition_Analysis.xlsx
+++ b/labs/lab-07-surface-attrition-insights-with-copilot-and-advanced-analysis/data/BrightPath_Attrition_Analysis.xlsx
@@ -68,7 +68,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -77,6 +77,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -22011,7 +22014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22054,7 +22057,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22066,12 +22068,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
@@ -22109,7 +22111,374 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>2 · A</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Chat</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>What's interesting about tblAttrition in relation to Left_Company? Give up to five patterns, each with the numbers and group sizes behind it. Do not change the workbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>2 · B</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Add the patterns you just gave me below the last row of Prompt_Log, one row each, with Decision set to "Unverified".</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>3 · C</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Chat</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>What is the overall attrition rate in tblAttrition (Left_Company = "Yes" divided by all employees)?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>3 · D</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>On a sheet named Checks (create it if needed), add these formulas with a label beside each, and tell me the results:
+=COUNTIFS(tblAttrition[Left_Company],"Yes")
+=COUNTIFS(tblAttrition[Left_Company],"Yes")/ROWS(tblAttrition[Employee_ID])</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>4 · E</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Chat</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Using tblAttrition, show attrition rate AND number of employees for:
+1) each Department;
+2) Engagement_Score below 3 vs 3 and above;
+3) Overtime_Hours_Month above 20 vs 20 or below;
+4) Years_Since_Promotion 3 or more vs below 3;
+5) Compa_Ratio below 0.9 vs 0.9 and above;
+6) each Work_Mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>4 · F</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>On the Checks sheet, add this formula for Engagement_Score below 3 and tell me if it matches:
+=COUNTIFS(tblAttrition[Engagement_Score],"&lt;3",tblAttrition[Left_Company],"Yes")/COUNTIFS(tblAttrition[Engagement_Score],"&lt;3")</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>5 · G</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Chat (advanced analysis)</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Enter advanced analysis mode. Compare employees who left with those who stayed on Overtime_Hours_Month, Engagement_Score, Years_Since_Promotion, Compa_Ratio and Training_Hours. Show the mean for each group, the group sizes, and the correlation between Overtime_Hours_Month and Engagement_Score. Explain the method.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>5 · H</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Chat (advanced analysis)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Which rows and columns does your code use, and how does it handle blanks?</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>5 · I</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>On the Checks sheet, add these formulas and tell me if they match your means for leavers:
+=AVERAGEIFS(tblAttrition[Overtime_Hours_Month],tblAttrition[Left_Company],"Yes")
+=AVERAGEIFS(tblAttrition[Engagement_Score],tblAttrition[Left_Company],"Yes")</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>6 · J</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Chat</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Here are my verified findings: &lt;paste your checked rates and means&gt;. For each, write one OBSERVED sentence with the numbers, one HYPOTHESIS that could explain it, and one limitation (sample size, correlation is not causation, overlapping factors). Keep each under 30 words.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>6 · K</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Write these four findings into the Insight_Log sheet, one per row, with the numbers, the OBSERVED or HYPOTHESIS label, the explanation to test and the limitation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>7 · L</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Chat</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Review my Insight_Log. Which statement overstates the evidence or implies causation? How would you reword it?</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>7 · M</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Prompt_Log already lists every prompt in this lab. For each one I ran, fill in What Copilot did and How I verified, and set Decision to Keep. I will tell you any row to change to Revise or Undo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Extra 1</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>What's interesting about this data in relation to Left_Company? Give five patterns with numbers and group sizes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Extra 2</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>What is the overall attrition rate in tblAttrition? Show the numerator and denominator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Extra 3</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Show attrition rate and headcount for Engagement_Score below 3 vs 3 and above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Extra 4</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Show attrition rate and number of employees by Department, sorted highest first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Extra 5</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Enter advanced analysis mode. Compare leavers and stayers on overtime, engagement, promotion, compa-ratio and training.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Extra 6</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>What is the correlation between Overtime_Hours_Month and Engagement_Score, and what does it mean for interpreting the attrition patterns?</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Extra 7</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Are there any managers (Manager_ID) whose teams have unusually high attrition? Only include teams with at least 10 people.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Extra 8</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Which of my insights could be a coincidence or caused by another factor? Explain.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
